--- a/trunk/plan/excel/成就表.xlsx
+++ b/trunk/plan/excel/成就表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20760" windowHeight="7545"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="AchieveCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/成就表.xlsx
+++ b/trunk/plan/excel/成就表.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowHeight="3960"/>
   </bookViews>
   <sheets>
     <sheet name="AchieveCFG" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -40,6 +38,15 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Reward</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
     <t>clientExe</t>
   </si>
   <si>
@@ -49,9 +56,6 @@
     <t>clientExe3</t>
   </si>
   <si>
-    <t>cs</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -67,7 +71,19 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>成就1</t>
+    <t>初出茅庐</t>
+  </si>
+  <si>
+    <t>成长</t>
+  </si>
+  <si>
+    <t>完成第一次收获</t>
+  </si>
+  <si>
+    <t>100金币</t>
+  </si>
+  <si>
+    <t>achieve_first</t>
   </si>
   <si>
     <t>1.11,1.12</t>
@@ -76,19 +92,130 @@
     <t>1,2,3,4,5</t>
   </si>
   <si>
-    <t>成就2</t>
-  </si>
-  <si>
-    <t>成就3</t>
-  </si>
-  <si>
-    <t>成就4</t>
-  </si>
-  <si>
-    <t>成就5</t>
-  </si>
-  <si>
-    <t>成就6</t>
+    <t>勤劳致富</t>
+  </si>
+  <si>
+    <t>累计收获100次作物</t>
+  </si>
+  <si>
+    <t>200金币 + 种子礼包</t>
+  </si>
+  <si>
+    <t>achieve_harvest</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>收获达人</t>
+  </si>
+  <si>
+    <t>单日收获达到50次</t>
+  </si>
+  <si>
+    <t>500金币 + 稀有种子</t>
+  </si>
+  <si>
+    <t>achieve_daily</t>
+  </si>
+  <si>
+    <t>金币收藏家</t>
+  </si>
+  <si>
+    <t>财富</t>
+  </si>
+  <si>
+    <t>累计获得10000金币</t>
+  </si>
+  <si>
+    <t>1000金币 + 金锄头</t>
+  </si>
+  <si>
+    <t>achieve_gold</t>
+  </si>
+  <si>
+    <t>土地开拓者</t>
+  </si>
+  <si>
+    <t>解锁第5块土地</t>
+  </si>
+  <si>
+    <t>新土地解锁券</t>
+  </si>
+  <si>
+    <t>achieve_land</t>
+  </si>
+  <si>
+    <t>作物大师</t>
+  </si>
+  <si>
+    <t>种植过10种不同作物</t>
+  </si>
+  <si>
+    <t>作物图鉴解锁</t>
+  </si>
+  <si>
+    <t>achieve_crop</t>
+  </si>
+  <si>
+    <t>连续登录</t>
+  </si>
+  <si>
+    <t>日常</t>
+  </si>
+  <si>
+    <t>连续登录7天</t>
+  </si>
+  <si>
+    <t>7日登录礼包</t>
+  </si>
+  <si>
+    <t>achieve_login</t>
+  </si>
+  <si>
+    <t>任务达人</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>完成20个任务</t>
+  </si>
+  <si>
+    <t>任务达人称号</t>
+  </si>
+  <si>
+    <t>achieve_task</t>
+  </si>
+  <si>
+    <t>完美主义者</t>
+  </si>
+  <si>
+    <t>成就</t>
+  </si>
+  <si>
+    <t>达成所有基础成就</t>
+  </si>
+  <si>
+    <t>完美成就徽章</t>
+  </si>
+  <si>
+    <t>achieve_perfect</t>
+  </si>
+  <si>
+    <t>传奇农夫</t>
+  </si>
+  <si>
+    <t>终极</t>
+  </si>
+  <si>
+    <t>达成全部成就</t>
+  </si>
+  <si>
+    <t>传奇农夫称号 + 限定皮肤</t>
+  </si>
+  <si>
+    <t>achieve_legend</t>
   </si>
 </sst>
 </file>
@@ -101,7 +228,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,158 +690,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -760,7 +890,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -770,7 +900,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -844,7 +974,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -879,7 +1008,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1056,15 +1184,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="4" max="4" width="10.375" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="10.375" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1083,134 +1206,337 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>1.1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <v>1.2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="9" spans="1:9">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>1.1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>